--- a/master/result/93_重生校园_追逐光芒/93_重生校园_追逐光芒.xlsx
+++ b/master/result/93_重生校园_追逐光芒/93_重生校园_追逐光芒.xlsx
@@ -397,434 +397,549 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:D38"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>rainbow</v>
       </c>
       <c r="B2" t="str">
-        <v>rainbow</v>
+        <v>/rainbow/</v>
       </c>
       <c r="C2" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>彩虹</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>porch</v>
       </c>
       <c r="B3" t="str">
-        <v>porch</v>
+        <v>/porch/</v>
       </c>
       <c r="C3" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>门廊</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>ten</v>
       </c>
       <c r="B4" t="str">
-        <v>ten</v>
+        <v>/ten/</v>
       </c>
       <c r="C4" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>十</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>disappoint</v>
       </c>
       <c r="B5" t="str">
-        <v>disappoint</v>
+        <v>/ˌdɪsəˈpɔɪnt/</v>
       </c>
       <c r="C5" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>失望</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>memory</v>
       </c>
       <c r="B6" t="str">
-        <v>memory</v>
+        <v>/memory/</v>
       </c>
       <c r="C6" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>记忆</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>rust</v>
       </c>
       <c r="B7" t="str">
-        <v>rust</v>
+        <v>/rust/</v>
       </c>
       <c r="C7" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>铁锈</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>safeguard</v>
       </c>
       <c r="B8" t="str">
-        <v>safeguard</v>
+        <v>/safeguard/</v>
       </c>
       <c r="C8" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>保护</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>concise</v>
       </c>
       <c r="B9" t="str">
-        <v>concise</v>
+        <v>/concise/</v>
       </c>
       <c r="C9" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>简洁的</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>humor</v>
       </c>
       <c r="B10" t="str">
-        <v>humor</v>
+        <v>/humor/</v>
       </c>
       <c r="C10" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>幽默</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>ecology</v>
       </c>
       <c r="B11" t="str">
-        <v>ecology</v>
+        <v>/ecology/</v>
       </c>
       <c r="C11" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>生态学</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>anyone</v>
       </c>
       <c r="B12" t="str">
-        <v>anyone</v>
+        <v>/anyone/</v>
       </c>
       <c r="C12" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>任何人</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>marine</v>
       </c>
       <c r="B13" t="str">
-        <v>marine</v>
+        <v>/marine/</v>
       </c>
       <c r="C13" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D13" t="str">
         <v>海的</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>oriental</v>
       </c>
       <c r="B14" t="str">
-        <v>oriental</v>
+        <v>/oriental/</v>
       </c>
       <c r="C14" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D14" t="str">
         <v>东方</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>compute</v>
       </c>
       <c r="B15" t="str">
-        <v>compute</v>
+        <v>/compute/</v>
       </c>
       <c r="C15" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>计算</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>incredible</v>
       </c>
       <c r="B16" t="str">
-        <v>incredible</v>
+        <v>/incredible/</v>
       </c>
       <c r="C16" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>不可思议</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>leisure</v>
       </c>
       <c r="B17" t="str">
-        <v>leisure</v>
+        <v>/leisure/</v>
       </c>
       <c r="C17" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>悠闲</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>anxious</v>
       </c>
       <c r="B18" t="str">
-        <v>anxious</v>
+        <v>/ˈæŋkʃəs/</v>
       </c>
       <c r="C18" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D18" t="str">
         <v>焦虑</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>bother</v>
       </c>
       <c r="B19" t="str">
-        <v>bother</v>
+        <v>/ˈbɒðə/</v>
       </c>
       <c r="C19" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>打扰</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>maybe</v>
       </c>
       <c r="B20" t="str">
-        <v>maybe</v>
+        <v>/maybe/</v>
       </c>
       <c r="C20" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>可能</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>self</v>
       </c>
       <c r="B21" t="str">
-        <v>self</v>
+        <v>/self/</v>
       </c>
       <c r="C21" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>自己</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>jacket</v>
       </c>
       <c r="B22" t="str">
-        <v>jacket</v>
+        <v>/jacket/</v>
       </c>
       <c r="C22" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>夹克</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>prosper</v>
       </c>
       <c r="B23" t="str">
-        <v>prosper</v>
+        <v>/prosper/</v>
       </c>
       <c r="C23" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>繁荣</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>silk</v>
       </c>
       <c r="B24" t="str">
-        <v>silk</v>
+        <v>/silk/</v>
       </c>
       <c r="C24" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>丝</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>stage</v>
       </c>
       <c r="B25" t="str">
+        <v>/stage/</v>
+      </c>
+      <c r="C25" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D25" t="str">
+        <v>舞台</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>omit</v>
+      </c>
+      <c r="B26" t="str">
+        <v>/omit/</v>
+      </c>
+      <c r="C26" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D26" t="str">
+        <v>省略</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>scandal</v>
+      </c>
+      <c r="B27" t="str">
+        <v>/scandal/</v>
+      </c>
+      <c r="C27" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D27" t="str">
+        <v>丑闻</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>preclude</v>
+      </c>
+      <c r="B28" t="str">
+        <v>/preclude/</v>
+      </c>
+      <c r="C28" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D28" t="str">
+        <v>阻止</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>weep</v>
+      </c>
+      <c r="B29" t="str">
+        <v>/wiːp/</v>
+      </c>
+      <c r="C29" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D29" t="str">
+        <v>哭泣</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>harvest</v>
+      </c>
+      <c r="B30" t="str">
+        <v>/harvest/</v>
+      </c>
+      <c r="C30" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D30" t="str">
+        <v>收获</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>bundle</v>
+      </c>
+      <c r="B31" t="str">
+        <v>/bundle/</v>
+      </c>
+      <c r="C31" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D31" t="str">
+        <v>捆</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>gift</v>
+      </c>
+      <c r="B32" t="str">
+        <v>/gift/</v>
+      </c>
+      <c r="C32" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D32" t="str">
+        <v>礼物</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>continent</v>
+      </c>
+      <c r="B33" t="str">
+        <v>/ˈkɒntɪnənt/</v>
+      </c>
+      <c r="C33" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D33" t="str">
+        <v>大陆</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>diagram</v>
+      </c>
+      <c r="B34" t="str">
+        <v>/diagram/</v>
+      </c>
+      <c r="C34" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D34" t="str">
+        <v>图表</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>era</v>
+      </c>
+      <c r="B35" t="str">
+        <v>/era/</v>
+      </c>
+      <c r="C35" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D35" t="str">
+        <v>时代</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>invert</v>
+      </c>
+      <c r="B36" t="str">
+        <v>/invert/</v>
+      </c>
+      <c r="C36" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D36" t="str">
+        <v>倒置</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
         <v>stage</v>
       </c>
-      <c r="C25" t="str">
-        <v>舞台</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="str">
-        <v>omit</v>
-      </c>
-      <c r="C26" t="str">
-        <v>省略</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="str">
-        <v>scandal</v>
-      </c>
-      <c r="C27" t="str">
-        <v>丑闻</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="str">
-        <v>preclude</v>
-      </c>
-      <c r="C28" t="str">
-        <v>阻止</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="str">
-        <v>weep</v>
-      </c>
-      <c r="C29" t="str">
-        <v>哭泣</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" t="str">
-        <v>harvest</v>
-      </c>
-      <c r="C30" t="str">
-        <v>收获</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" t="str">
-        <v>bundle</v>
-      </c>
-      <c r="C31" t="str">
-        <v>捆</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="str">
-        <v>gift</v>
-      </c>
-      <c r="C32" t="str">
-        <v>礼物</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="str">
-        <v>continent</v>
-      </c>
-      <c r="C33" t="str">
-        <v>大陆</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="str">
-        <v>diagram</v>
-      </c>
-      <c r="C34" t="str">
-        <v>图表</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="str">
-        <v>era</v>
-      </c>
-      <c r="C35" t="str">
-        <v>时代</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="str">
-        <v>invert</v>
-      </c>
-      <c r="C36" t="str">
-        <v>倒置</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37">
-        <v>36</v>
-      </c>
       <c r="B37" t="str">
-        <v>stage</v>
+        <v>/stage/</v>
       </c>
       <c r="C37" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D37" t="str">
         <v>阶段</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>county</v>
       </c>
       <c r="B38" t="str">
-        <v>county</v>
+        <v>/ˈkaʊnti/</v>
       </c>
       <c r="C38" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D38" t="str">
         <v>县</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C38"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D38"/>
   </ignoredErrors>
 </worksheet>
 </file>